--- a/Result/profitability/5484.xlsx
+++ b/Result/profitability/5484.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07375</v>
+        <v>0.05000000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>25.81</v>
+        <v>23.905</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0425</v>
+        <v>0.1325</v>
       </c>
       <c r="N3" t="n">
-        <v>26.49625</v>
+        <v>24.33875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0.13875</v>
+        <v>0.28625</v>
       </c>
       <c r="N4" t="n">
-        <v>26.67</v>
+        <v>26.30625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>0.26625</v>
+        <v>0.38875</v>
       </c>
       <c r="N5" t="n">
-        <v>28.42875</v>
+        <v>27.08375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.365</v>
+        <v>0.3825</v>
       </c>
       <c r="N6" t="n">
-        <v>29.8625</v>
+        <v>29.035</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0.38875</v>
+        <v>0.44625</v>
       </c>
       <c r="N7" t="n">
-        <v>32.36375</v>
+        <v>31.24375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4525</v>
+        <v>0.47875</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3925</v>
+        <v>34.22625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>267</v>
+      </c>
+      <c r="D75" t="n">
+        <v>227</v>
+      </c>
+      <c r="E75" t="n">
+        <v>40</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>51</v>
+      </c>
+      <c r="J75" t="n">
+        <v>36</v>
+      </c>
+      <c r="K75" t="n">
+        <v>36</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.04499999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.985</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6363636363636365</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08094948265368229</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.227272727272728</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-10.76</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4160866202629544</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
